--- a/AAII_Financials/Quarterly/MNMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNMD_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>MNMD</t>
   </si>
@@ -656,65 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -745,8 +748,11 @@
       <c r="L8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -777,8 +783,11 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +818,11 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,40 +835,44 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E12" s="3">
         <v>7600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>14000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>34800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,8 +903,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -916,11 +935,14 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -945,14 +967,17 @@
       <c r="J15" s="3">
         <v>800</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="3">
+      <c r="K15" s="3">
+        <v>800</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,40 +987,44 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E17" s="3">
         <v>21600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>20900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>93900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17200</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1003,31 +1032,34 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-29200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-20900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-17000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-18500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-93900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,8 +1072,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1049,31 +1082,34 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>9000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1081,54 +1117,57 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-28300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-24000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-15700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-91600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1136,40 +1175,46 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-29100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-24800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-16500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-18500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-94200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1182,8 +1227,8 @@
       <c r="F24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
@@ -1191,17 +1236,20 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3">
         <v>-1200</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1280,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-29100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-24800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-16500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-18500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-93000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-29100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-24800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-16500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-18500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-93000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1385,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1420,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1455,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,8 +1490,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1433,63 +1502,69 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-9000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-29100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-24800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-16500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-18500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-93000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1595,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-29100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-24800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-16500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-18500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-93000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1687,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,40 +1702,44 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>99700</v>
+      </c>
+      <c r="E41" s="3">
         <v>117700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>116900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>129400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>142100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>154500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>105700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>120500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>133500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>145900</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1681,8 +1770,11 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1713,8 +1805,11 @@
       <c r="L43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1745,72 +1840,81 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E45" s="3">
         <v>2400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>103900</v>
+      </c>
+      <c r="E46" s="3">
         <v>120100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>119800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>132400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>146100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>156500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>109100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>123200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>137200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1841,8 +1945,11 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1867,46 +1974,52 @@
       <c r="J48" s="3">
         <v>0</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="K48" s="3">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E49" s="3">
         <v>21200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>24400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>25200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>26000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>26800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2050,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,8 +2085,11 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -1978,7 +2097,7 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>300</v>
@@ -1986,8 +2105,8 @@
       <c r="G52" s="3">
         <v>300</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
+      <c r="H52" s="3">
+        <v>300</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>4</v>
@@ -2001,8 +2120,11 @@
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2155,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>124500</v>
+      </c>
+      <c r="E54" s="3">
         <v>141600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>142100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>155500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>170000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>180900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>134300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>149200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>164000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>178600</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2207,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,40 +2222,44 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E57" s="3">
         <v>7700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2157,72 +2290,81 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E59" s="3">
         <v>23500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>26500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6200</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E60" s="3">
         <v>31200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>35100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>24100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2230,7 +2372,7 @@
         <v>14100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>14100</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -2253,28 +2395,31 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
         <v>300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1300</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1900</v>
       </c>
       <c r="J62" s="3">
         <v>1900</v>
@@ -2283,10 +2428,13 @@
         <v>1900</v>
       </c>
       <c r="L62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M62" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2465,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2500,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2535,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E66" s="3">
         <v>45600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>36100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>27300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2587,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2620,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2655,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2690,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +2725,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-290200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-266300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-248400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-219300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-194500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-189600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-173100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-156100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-137700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-94000</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2795,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +2830,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +2865,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>78100</v>
+      </c>
+      <c r="E76" s="3">
         <v>96000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>106000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>130300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>150900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>153600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>124500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>136800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>151700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>166000</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +2935,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-29100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-24800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-16500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-18500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-93000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,8 +3027,9 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2857,13 +3055,16 @@
         <v>800</v>
       </c>
       <c r="K83" s="3">
+        <v>800</v>
+      </c>
+      <c r="L83" s="3">
         <v>2600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3095,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3130,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3165,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3200,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3235,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-16600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-12800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-15100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-45800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10800</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,8 +3287,9 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3100,8 +3320,11 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3355,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,19 +3390,22 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
@@ -3191,13 +3420,16 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,8 +3442,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3242,8 +3475,11 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3510,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3545,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,40 +3580,46 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E100" s="3">
         <v>17400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>58200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>98800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3379,59 +3627,65 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E102" s="3">
         <v>800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-12400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>48800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>53400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MNMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>MNMD</t>
   </si>
@@ -656,68 +656,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -751,8 +755,11 @@
       <c r="M8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -786,8 +793,11 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -821,8 +831,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,43 +849,47 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E12" s="3">
         <v>20200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>34800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,31 +923,34 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
@@ -938,16 +958,19 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
         <v>800</v>
@@ -970,14 +993,17 @@
       <c r="K15" s="3">
         <v>800</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="L15" s="3">
+        <v>800</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,8 +1014,9 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -997,34 +1024,37 @@
         <v>22200</v>
       </c>
       <c r="E17" s="3">
+        <v>22200</v>
+      </c>
+      <c r="F17" s="3">
         <v>21600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>29200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>20900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>93900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17200</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1032,34 +1062,37 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-21600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-29200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-20900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-17000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-18500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-93900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1073,8 +1106,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1082,34 +1116,37 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F20" s="3">
         <v>3900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>9000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1117,46 +1154,49 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-16900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-28300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-24000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-15700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-91600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3">
         <v>500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1169,8 +1209,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1178,43 +1218,49 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-23900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-29100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-18500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-94200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1230,8 +1276,8 @@
       <c r="G24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
@@ -1239,17 +1285,20 @@
       <c r="J24" s="3">
         <v>0</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3">
         <v>-1200</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,78 +1332,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-23900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-29100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-24800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-18500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-93000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-29100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-24800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-18500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-93000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,8 +1446,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1423,8 +1484,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1522,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,8 +1560,11 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1502,69 +1572,75 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-9000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-29100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-24800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-18500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-93000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,83 +1674,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-29100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-24800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-18500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-93000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +1773,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,43 +1789,47 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>252300</v>
+      </c>
+      <c r="E41" s="3">
         <v>99700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>117700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>116900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>129400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>142100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>154500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>105700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>120500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>133500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>145900</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1773,8 +1863,11 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1808,8 +1901,11 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1843,78 +1939,87 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E45" s="3">
         <v>4200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>255500</v>
+      </c>
+      <c r="E46" s="3">
         <v>103900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>120100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>119800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>132400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>146100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>156500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>109100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>123200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>137200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1948,8 +2053,11 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1977,49 +2085,55 @@
       <c r="K48" s="3">
         <v>0</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E49" s="3">
         <v>20400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>21200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>22800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>24400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>25200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>26000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>26800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2167,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,19 +2205,22 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
       </c>
       <c r="F52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G52" s="3">
         <v>300</v>
@@ -2108,8 +2228,8 @@
       <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
+      <c r="I52" s="3">
+        <v>300</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>4</v>
@@ -2123,8 +2243,11 @@
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,43 +2281,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>275500</v>
+      </c>
+      <c r="E54" s="3">
         <v>124500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>141600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>142100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>155500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>170000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>180900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>134300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>149200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>164000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>178600</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2337,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,43 +2353,47 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E57" s="3">
         <v>4100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2293,89 +2427,98 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E59" s="3">
         <v>28100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>23500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>26500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6200</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E60" s="3">
         <v>32200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>31200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>24100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14100</v>
+        <v>14200</v>
       </c>
       <c r="E61" s="3">
         <v>14100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>14100</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2398,8 +2541,11 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2407,22 +2553,22 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
         <v>300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1300</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1900</v>
       </c>
       <c r="K62" s="3">
         <v>1900</v>
@@ -2431,10 +2577,13 @@
         <v>1900</v>
       </c>
       <c r="M62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N62" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +2617,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +2655,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,43 +2693,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>79500</v>
+      </c>
+      <c r="E66" s="3">
         <v>46400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>45600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>36100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +2749,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +2785,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +2823,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2693,8 +2861,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,43 +2899,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-344600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-290200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-266300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-248400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-219300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-194500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-189600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-173100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-156100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-137700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-94000</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +2975,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3013,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,43 +3051,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>196100</v>
+      </c>
+      <c r="E76" s="3">
         <v>78100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>96000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>106000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>130300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>150900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>153600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>124500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>136800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>151700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>166000</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,83 +3127,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-29100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-24800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-18500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-93000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,13 +3226,14 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E83" s="3">
         <v>800</v>
@@ -3058,13 +3257,16 @@
         <v>800</v>
       </c>
       <c r="L83" s="3">
+        <v>800</v>
+      </c>
+      <c r="M83" s="3">
         <v>2600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +3300,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +3338,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +3376,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +3414,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,43 +3452,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-20600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-16600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-12800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-9300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-15100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-12900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-45800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10800</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,8 +3508,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3323,8 +3544,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +3582,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,8 +3620,11 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3423,13 +3653,16 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,8 +3676,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3478,8 +3712,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +3750,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +3788,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,43 +3826,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>169200</v>
+      </c>
+      <c r="E100" s="3">
         <v>2600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>17400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>58200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>98800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3630,62 +3879,68 @@
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>152600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-18000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-12700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-12400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>48800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>53400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MNMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>MNMD</t>
   </si>
@@ -656,72 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -758,8 +762,11 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -796,8 +803,11 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -834,8 +844,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,46 +863,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E12" s="3">
         <v>11200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>34800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,34 +943,37 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
+        <v>-2500</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
@@ -961,19 +981,22 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>800</v>
       </c>
       <c r="F15" s="3">
         <v>800</v>
@@ -996,14 +1019,17 @@
       <c r="L15" s="3">
         <v>800</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="3">
+      <c r="M15" s="3">
+        <v>800</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,46 +1041,50 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>22200</v>
+        <v>21900</v>
       </c>
       <c r="E17" s="3">
         <v>22200</v>
       </c>
       <c r="F17" s="3">
+        <v>22200</v>
+      </c>
+      <c r="G17" s="3">
         <v>21600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>29200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>20900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>93900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17200</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1065,34 +1095,37 @@
         <v>-22200</v>
       </c>
       <c r="F18" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="G18" s="3">
         <v>-21600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-29200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-20900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-17000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-16900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-18500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-93900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,8 +1140,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1116,37 +1150,40 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1154,52 +1191,55 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-53900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-22600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-16900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-28300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-24000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-15700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-16100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-91600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>4</v>
       </c>
@@ -1212,8 +1252,8 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1221,46 +1261,52 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-54400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-23900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-29100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-24800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-17000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-94200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1279,8 +1325,8 @@
       <c r="H24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -1288,17 +1334,20 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3">
         <v>-1200</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,84 +1384,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-54400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-23900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-29100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-24800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-17000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-18500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-93000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-54400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-29100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-24800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-17000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-18500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-93000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1487,8 +1548,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,8 +1630,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1572,75 +1642,81 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>32200</v>
+      </c>
+      <c r="F32" s="3">
         <v>1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-54400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-29100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-24800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-17000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-18500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-93000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,89 +1753,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-54400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-29100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-24800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-17000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-18500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-93000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,46 +1876,50 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>243100</v>
+      </c>
+      <c r="E41" s="3">
         <v>252300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>99700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>117700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>116900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>129400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>142100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>154500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>105700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>120500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>133500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>145900</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1866,8 +1956,11 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1904,8 +1997,11 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1942,84 +2038,93 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E45" s="3">
         <v>3100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>247700</v>
+      </c>
+      <c r="E46" s="3">
         <v>255500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>103900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>120100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>119800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>132400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>146100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>156500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>109100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>123200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>137200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2056,8 +2161,11 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2088,14 +2196,17 @@
       <c r="L48" s="3">
         <v>0</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2103,37 +2214,40 @@
         <v>19900</v>
       </c>
       <c r="E49" s="3">
+        <v>19900</v>
+      </c>
+      <c r="F49" s="3">
         <v>20400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>21200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>22000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>22800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>23600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>24400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>25200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>26000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>26800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,22 +2325,25 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>500</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>200</v>
       </c>
       <c r="G52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H52" s="3">
         <v>300</v>
@@ -2231,8 +2351,8 @@
       <c r="I52" s="3">
         <v>300</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
+      <c r="J52" s="3">
+        <v>300</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
@@ -2246,8 +2366,11 @@
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,46 +2407,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>268100</v>
+      </c>
+      <c r="E54" s="3">
         <v>275500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>124500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>141600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>142100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>155500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>170000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>180900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>134300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>149200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>164000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>178600</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,46 +2484,50 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E57" s="3">
         <v>7600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2430,98 +2564,107 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E59" s="3">
         <v>57700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>28100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>26500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>25200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E60" s="3">
         <v>65300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>31200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>35100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>24100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E61" s="3">
         <v>14200</v>
-      </c>
-      <c r="E61" s="3">
-        <v>14100</v>
       </c>
       <c r="F61" s="3">
         <v>14100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>14100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2544,8 +2687,11 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2556,22 +2702,22 @@
         <v>0</v>
       </c>
       <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
         <v>300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1300</v>
-      </c>
-      <c r="K62" s="3">
-        <v>1900</v>
       </c>
       <c r="L62" s="3">
         <v>1900</v>
@@ -2580,10 +2726,13 @@
         <v>1900</v>
       </c>
       <c r="N62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O62" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,46 +2851,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>66100</v>
+      </c>
+      <c r="E66" s="3">
         <v>79500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>46400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>19100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>27300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2864,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,46 +3073,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-350500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-344600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-290200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-266300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-248400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-219300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-194500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-189600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-173100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-156100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-137700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-94000</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>202000</v>
+      </c>
+      <c r="E76" s="3">
         <v>196100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>78100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>96000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>106000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>130300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>150900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>153600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>124500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>136800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>151700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>166000</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,89 +3319,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-54400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-29100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-24800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-17000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-18500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-93000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,16 +3425,17 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
         <v>500</v>
-      </c>
-      <c r="E83" s="3">
-        <v>800</v>
       </c>
       <c r="F83" s="3">
         <v>800</v>
@@ -3260,13 +3459,16 @@
         <v>800</v>
       </c>
       <c r="M83" s="3">
+        <v>800</v>
+      </c>
+      <c r="N83" s="3">
         <v>2600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-16600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-20600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-16600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-13300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-15100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-12900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-45800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10800</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,8 +3729,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3547,8 +3768,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,8 +3850,11 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3656,13 +3886,16 @@
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,8 +3910,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3715,8 +3949,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,46 +4072,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E100" s="3">
         <v>169200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>17400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>58200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>98800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3882,65 +4131,71 @@
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="E102" s="3">
         <v>152600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-18000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-12500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-12700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>48800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-14700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>53400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MNMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>MNMD</t>
   </si>
@@ -656,99 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -765,8 +769,11 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -806,8 +813,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -847,8 +857,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,49 +877,53 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E12" s="3">
         <v>14600</v>
       </c>
-      <c r="E12" s="3">
-        <v>11200</v>
-      </c>
       <c r="F12" s="3">
-        <v>20200</v>
+        <v>11700</v>
       </c>
       <c r="G12" s="3">
-        <v>7600</v>
+        <v>11500</v>
       </c>
       <c r="H12" s="3">
-        <v>14000</v>
+        <v>13200</v>
       </c>
       <c r="I12" s="3">
-        <v>11800</v>
+        <v>14800</v>
       </c>
       <c r="J12" s="3">
+        <v>12600</v>
+      </c>
+      <c r="K12" s="3">
         <v>8000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>9400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>34800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,17 +963,20 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
         <v>-2500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
@@ -972,11 +992,11 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
@@ -984,11 +1004,14 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -996,22 +1019,22 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>800</v>
@@ -1022,14 +1045,17 @@
       <c r="M15" s="3">
         <v>800</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="3">
+      <c r="N15" s="3">
+        <v>800</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1068,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>21900</v>
+        <v>24800</v>
       </c>
       <c r="E17" s="3">
-        <v>22200</v>
+        <v>24500</v>
       </c>
       <c r="F17" s="3">
         <v>22200</v>
       </c>
       <c r="G17" s="3">
+        <v>22200</v>
+      </c>
+      <c r="H17" s="3">
         <v>21600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>29200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>93900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17200</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-24800</v>
       </c>
       <c r="E18" s="3">
-        <v>-22200</v>
+        <v>-24500</v>
       </c>
       <c r="F18" s="3">
         <v>-22200</v>
       </c>
       <c r="G18" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="H18" s="3">
         <v>-21600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-29200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-20900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-17000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-16900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-18500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-93900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,113 +1174,120 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>-8300</v>
       </c>
       <c r="E20" s="3">
-        <v>-32200</v>
+        <v>-13400</v>
       </c>
       <c r="F20" s="3">
-        <v>-1200</v>
+        <v>33400</v>
       </c>
       <c r="G20" s="3">
-        <v>3900</v>
+        <v>2600</v>
       </c>
       <c r="H20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J20" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K20" s="3">
+        <v>9000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>500</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>9000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>500</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-16500</v>
       </c>
       <c r="E21" s="3">
-        <v>-53900</v>
+        <v>-11000</v>
       </c>
       <c r="F21" s="3">
-        <v>-22600</v>
+        <v>-55600</v>
       </c>
       <c r="G21" s="3">
-        <v>-16900</v>
+        <v>-24800</v>
       </c>
       <c r="H21" s="3">
-        <v>-28300</v>
+        <v>-19100</v>
       </c>
       <c r="I21" s="3">
-        <v>-24000</v>
+        <v>-30400</v>
       </c>
       <c r="J21" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-4100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-15700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-17700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-91600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
+      <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
+        <v>500</v>
       </c>
       <c r="F22" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G22" s="3">
-        <v>200</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
+        <v>-200</v>
+      </c>
+      <c r="H22" s="3">
+        <v>300</v>
+      </c>
+      <c r="I22" s="3">
+        <v>100</v>
+      </c>
+      <c r="J22" s="3">
+        <v>100</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
@@ -1255,8 +1295,8 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1264,49 +1304,55 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-54400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-23900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-29100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-24800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-17000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-94200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1328,8 +1374,8 @@
       <c r="I24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1337,17 +1383,20 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3">
         <v>-1200</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1436,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-54400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-29100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-24800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-17000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-93000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-54400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-29100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-24800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-93000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1568,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1612,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1656,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,90 +1700,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>8300</v>
       </c>
       <c r="E32" s="3">
-        <v>32200</v>
+        <v>13400</v>
       </c>
       <c r="F32" s="3">
-        <v>1200</v>
+        <v>-33400</v>
       </c>
       <c r="G32" s="3">
-        <v>-3900</v>
+        <v>-2600</v>
       </c>
       <c r="H32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>4000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-54400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-29100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-24800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-18500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-93000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1832,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-54400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-29100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-24800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-18500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-93000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +1945,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,49 +1963,53 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>295300</v>
+      </c>
+      <c r="E41" s="3">
         <v>243100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>252300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>99700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>117700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>116900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>129400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>142100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>154500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>105700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>120500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>133500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>145900</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1959,31 +2049,34 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2000,31 +2093,34 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2041,113 +2137,122 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>4600</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2900</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>3900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>299400</v>
+      </c>
+      <c r="E46" s="3">
         <v>247700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>255500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>103900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>120100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>119800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>132400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>146100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>156500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>109100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>123200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>137200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2164,31 +2269,34 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -2199,14 +2307,17 @@
       <c r="M48" s="3">
         <v>0</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2217,37 +2328,40 @@
         <v>19900</v>
       </c>
       <c r="F49" s="3">
+        <v>19900</v>
+      </c>
+      <c r="G49" s="3">
         <v>20400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>21200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>22000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>22800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>23600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>24400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>25200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>26000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>26800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2401,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,8 +2445,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2337,16 +2457,16 @@
         <v>500</v>
       </c>
       <c r="E52" s="3">
+        <v>500</v>
+      </c>
+      <c r="F52" s="3">
         <v>100</v>
-      </c>
-      <c r="F52" s="3">
-        <v>200</v>
       </c>
       <c r="G52" s="3">
         <v>200</v>
       </c>
       <c r="H52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I52" s="3">
         <v>300</v>
@@ -2354,8 +2474,8 @@
       <c r="J52" s="3">
         <v>300</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
+      <c r="K52" s="3">
+        <v>300</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
@@ -2369,8 +2489,11 @@
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2533,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>319800</v>
+      </c>
+      <c r="E54" s="3">
         <v>268100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>275500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>124500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>141600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>142100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>155500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>170000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>180900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>134300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>149200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>164000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>178600</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2597,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,49 +2615,53 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2547,10 +2681,10 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2567,90 +2701,99 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>38900</v>
+        <v>22300</v>
       </c>
       <c r="E59" s="3">
-        <v>57700</v>
+        <v>30700</v>
       </c>
       <c r="F59" s="3">
-        <v>28100</v>
+        <v>47700</v>
       </c>
       <c r="G59" s="3">
-        <v>23500</v>
+        <v>16500</v>
       </c>
       <c r="H59" s="3">
-        <v>26500</v>
+        <v>13500</v>
       </c>
       <c r="I59" s="3">
-        <v>21800</v>
+        <v>16600</v>
       </c>
       <c r="J59" s="3">
+        <v>15100</v>
+      </c>
+      <c r="K59" s="3">
         <v>15800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6200</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E60" s="3">
         <v>41800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>65300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>31200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>35100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>24100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2658,16 +2801,16 @@
         <v>24300</v>
       </c>
       <c r="E61" s="3">
+        <v>24300</v>
+      </c>
+      <c r="F61" s="3">
         <v>14200</v>
-      </c>
-      <c r="F61" s="3">
-        <v>14100</v>
       </c>
       <c r="G61" s="3">
         <v>14100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>14100</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2690,37 +2833,40 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
       </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1300</v>
-      </c>
-      <c r="L62" s="3">
-        <v>1900</v>
       </c>
       <c r="M62" s="3">
         <v>1900</v>
@@ -2729,10 +2875,13 @@
         <v>1900</v>
       </c>
       <c r="O62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P62" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +2921,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +2965,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3009,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E66" s="3">
         <v>66100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>79500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>46400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>45600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>36100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3073,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3115,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3159,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3203,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3247,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-364100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-350500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-344600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-290200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-266300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-248400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-219300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-194500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-189600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-173100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-156100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-137700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-94000</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3335,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3379,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3423,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>262200</v>
+      </c>
+      <c r="E76" s="3">
         <v>202000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>196100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>78100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>96000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>106000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>130300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>150900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>153600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>124500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>136800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>151700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>166000</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3511,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-54400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-29100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-24800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-18500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-93000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,8 +3624,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3435,22 +3634,22 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>800</v>
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G83" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>800</v>
-      </c>
-      <c r="I83" s="3">
-        <v>800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>800</v>
+        <v>0</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>800</v>
@@ -3462,13 +3661,16 @@
         <v>800</v>
       </c>
       <c r="N83" s="3">
+        <v>800</v>
+      </c>
+      <c r="O83" s="3">
         <v>2600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3710,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3754,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +3798,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +3842,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +3886,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-20000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-16600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-20600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-16600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-13800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-15100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-12900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-45800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10800</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,31 +3950,32 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3771,8 +3992,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4036,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,31 +4080,34 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -3889,13 +4119,16 @@
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,31 +4144,32 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3952,8 +4186,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4230,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4274,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,49 +4318,55 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E100" s="3">
         <v>10800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>169200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>17400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>58200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>98800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4125,77 +4374,83 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>100</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>152600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-12500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>48800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>53400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MNMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>MNMD</t>
   </si>
@@ -656,80 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -754,8 +757,8 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -772,8 +775,11 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +822,11 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -860,8 +869,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,52 +890,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E12" s="3">
         <v>17200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>14600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>13200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>14800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>9400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>34800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,20 +982,23 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>-2500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
@@ -995,11 +1014,11 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
@@ -1007,11 +1026,14 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1037,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>800</v>
@@ -1048,14 +1070,17 @@
       <c r="N15" s="3">
         <v>800</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="3">
+      <c r="O15" s="3">
+        <v>800</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1094,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E17" s="3">
         <v>24800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24500</v>
-      </c>
-      <c r="F17" s="3">
-        <v>22200</v>
       </c>
       <c r="G17" s="3">
         <v>22200</v>
       </c>
       <c r="H17" s="3">
+        <v>22200</v>
+      </c>
+      <c r="I17" s="3">
         <v>21600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>29200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>93900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17200</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-24800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-24500</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-22200</v>
       </c>
       <c r="G18" s="3">
         <v>-22200</v>
       </c>
       <c r="H18" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-21600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-29200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-20900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-17000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-16900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-18500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-93900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,96 +1207,103 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-8300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-13400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>33400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-37400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-16500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-55600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-24800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-19100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-30400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-26100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-15700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-16100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-17700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-91600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1272,25 +1311,25 @@
         <v>700</v>
       </c>
       <c r="E22" s="3">
+        <v>700</v>
+      </c>
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>400</v>
       </c>
-      <c r="G22" s="3">
-        <v>-200</v>
-      </c>
       <c r="H22" s="3">
+        <v>400</v>
+      </c>
+      <c r="I22" s="3">
         <v>300</v>
-      </c>
-      <c r="I22" s="3">
-        <v>100</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
+      <c r="K22" s="3">
+        <v>100</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>4</v>
@@ -1298,8 +1337,8 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1307,52 +1346,58 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-54400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-23900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-17900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-29100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-24800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-17000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-94200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1377,8 +1422,8 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1386,17 +1431,20 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3">
         <v>-1200</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1487,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-54400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-29100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-24800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-17000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-93000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-13700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-54400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-23900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-29100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-24800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-17000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-93000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,8 +1628,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1615,8 +1675,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1722,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1769,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E32" s="3">
         <v>8300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>13400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-33400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-13700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-54400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-29100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-24800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-17000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-93000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1910,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-13700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-54400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-29100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-24800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-17000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-93000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2030,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,52 +2049,56 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>273700</v>
+      </c>
+      <c r="E41" s="3">
         <v>295300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>243100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>252300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>99700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>117700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>116900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>129400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>142100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>154500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>105700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>120500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>133500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>145900</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,8 +2141,11 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2078,8 +2170,8 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2096,8 +2188,11 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2122,8 +2217,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2140,8 +2235,11 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2166,70 +2264,76 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>3900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>281600</v>
+      </c>
+      <c r="E46" s="3">
         <v>299400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>247700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>255500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>103900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>120100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>119800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>132400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>146100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>156500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>109100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>123200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>137200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2254,8 +2358,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2272,8 +2376,11 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2298,8 +2405,8 @@
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -2310,14 +2417,17 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2331,37 +2441,40 @@
         <v>19900</v>
       </c>
       <c r="G49" s="3">
+        <v>19900</v>
+      </c>
+      <c r="H49" s="3">
         <v>20400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>21200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>22000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>23600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>24400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>25200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>26000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>26800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2517,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,28 +2564,31 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E52" s="3">
         <v>500</v>
       </c>
       <c r="F52" s="3">
+        <v>500</v>
+      </c>
+      <c r="G52" s="3">
         <v>100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>200</v>
       </c>
       <c r="H52" s="3">
         <v>200</v>
       </c>
       <c r="I52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J52" s="3">
         <v>300</v>
@@ -2477,8 +2596,8 @@
       <c r="K52" s="3">
         <v>300</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
+      <c r="L52" s="3">
+        <v>300</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
@@ -2492,8 +2611,11 @@
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2658,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>302200</v>
+      </c>
+      <c r="E54" s="3">
         <v>319800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>268100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>275500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>124500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>141600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>142100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>155500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>170000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>180900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>134300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>149200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>164000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>178600</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2726,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,52 +2745,56 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2681,13 +2814,13 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>100</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2704,116 +2837,125 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E59" s="3">
         <v>22300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>30700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>47700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>25200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6200</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E60" s="3">
         <v>33300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>41800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>65300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>31200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>35100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>24100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>24300</v>
+        <v>21900</v>
       </c>
       <c r="E61" s="3">
         <v>24300</v>
       </c>
       <c r="F61" s="3">
+        <v>24300</v>
+      </c>
+      <c r="G61" s="3">
         <v>14200</v>
-      </c>
-      <c r="G61" s="3">
-        <v>14100</v>
       </c>
       <c r="H61" s="3">
         <v>14100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>14100</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2836,8 +2978,11 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2847,29 +2992,29 @@
       <c r="E62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G62" s="3">
         <v>0</v>
       </c>
       <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
         <v>300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1300</v>
-      </c>
-      <c r="M62" s="3">
-        <v>1900</v>
       </c>
       <c r="N62" s="3">
         <v>1900</v>
@@ -2878,10 +3023,13 @@
         <v>1900</v>
       </c>
       <c r="P62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q62" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3072,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3119,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3166,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E66" s="3">
         <v>57600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>66100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>79500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>46400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>45600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>36100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3234,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3279,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3326,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3373,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3420,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-398900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-364100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-350500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-344600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-290200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-266300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-248400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-219300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-194500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-189600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-173100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-156100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-137700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-94000</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3514,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3561,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3608,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>241400</v>
+      </c>
+      <c r="E76" s="3">
         <v>262200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>202000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>196100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>78100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>96000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>106000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>130300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>150900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>153600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>124500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>136800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>151700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>166000</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3702,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-13700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-54400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-29100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-24800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-17000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-93000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,8 +3822,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3636,23 +3834,23 @@
       <c r="E83" s="3">
         <v>0</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
-        <v>800</v>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L83" s="3">
         <v>800</v>
@@ -3664,13 +3862,16 @@
         <v>800</v>
       </c>
       <c r="O83" s="3">
+        <v>800</v>
+      </c>
+      <c r="P83" s="3">
         <v>2600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3914,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3961,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4008,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4055,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4102,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-17200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-20000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-16600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-20600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-16600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-12800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-12900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-45800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-10800</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,8 +4170,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3977,8 +4197,8 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -3995,8 +4215,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4262,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,8 +4309,11 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4109,8 +4338,8 @@
       <c r="J94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -4122,13 +4351,16 @@
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4377,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4171,8 +4404,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4189,8 +4422,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4469,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4516,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +4563,58 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E100" s="3">
         <v>69400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>10800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>169200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>17400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>58200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>98800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4374,83 +4622,89 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E102" s="3">
         <v>52200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>152600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-18000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>48800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>53400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-11200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MNMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
   <si>
     <t>MNMD</t>
   </si>
@@ -656,83 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -760,8 +764,8 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -778,8 +782,11 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -825,8 +832,11 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -872,8 +882,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,55 +904,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E12" s="3">
         <v>21800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>17200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>13200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>14800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>34800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,23 +1002,26 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>-2500</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1017,11 +1037,11 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>4</v>
@@ -1029,11 +1049,14 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1050,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -1062,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3">
         <v>800</v>
@@ -1073,14 +1096,17 @@
       <c r="O15" s="3">
         <v>800</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="P15" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,102 +1121,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E17" s="3">
         <v>32500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>22200</v>
       </c>
       <c r="H17" s="3">
         <v>22200</v>
       </c>
       <c r="I17" s="3">
+        <v>22200</v>
+      </c>
+      <c r="J17" s="3">
         <v>21600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>29200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>93900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17200</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-32500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-24800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-24500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-22200</v>
       </c>
       <c r="H18" s="3">
         <v>-22200</v>
       </c>
       <c r="I18" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="J18" s="3">
         <v>-21600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-29200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-20900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-17000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-16900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-18500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-93900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,131 +1241,138 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E20" s="3">
         <v>4900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-13400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>33400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>9000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-37400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-16500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-55600</v>
-      </c>
       <c r="H21" s="3">
+        <v>-55100</v>
+      </c>
+      <c r="I21" s="3">
         <v>-24800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-19100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-30400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-15700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-16100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-17700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-91600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E22" s="3">
         <v>700</v>
       </c>
       <c r="F22" s="3">
+        <v>700</v>
+      </c>
+      <c r="G22" s="3">
         <v>500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>400</v>
       </c>
       <c r="H22" s="3">
         <v>400</v>
       </c>
       <c r="I22" s="3">
+        <v>400</v>
+      </c>
+      <c r="J22" s="3">
         <v>300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
+      <c r="L22" s="3">
+        <v>100</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>4</v>
@@ -1340,8 +1380,8 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1349,55 +1389,61 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-34700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-54400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-23900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-29100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-24800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-17000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-94200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1425,8 +1471,8 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1434,17 +1480,20 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-34700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-54400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-23900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-29100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-24800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-16500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-17000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-93000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-34700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-54400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-23900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-29100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-24800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-17000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-93000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,102 +1839,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>13400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-33400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-9000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-34700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-54400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-23900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-29100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-24800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-17000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-93000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-34700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-54400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-23900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-29100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-24800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-17000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-93000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,60 +2136,64 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>82900</v>
+      </c>
+      <c r="E41" s="3">
         <v>273700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>295300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>243100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>252300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>99700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>117700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>116900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>129400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>142100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>154500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>105700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>120500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>133500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>145900</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>129600</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2144,8 +2234,11 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2173,8 +2266,8 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2191,8 +2284,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2220,8 +2316,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2238,8 +2334,11 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2267,78 +2366,84 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>3900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>221700</v>
+      </c>
+      <c r="E46" s="3">
         <v>281600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>299400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>247700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>255500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>103900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>120100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>119800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>132400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>146100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>156500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>109100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>123200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>137200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>4</v>
+      <c r="D47" s="3">
+        <v>33100</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>4</v>
@@ -2361,8 +2466,8 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2379,8 +2484,11 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2408,8 +2516,8 @@
       <c r="K48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -2420,14 +2528,17 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2444,37 +2555,40 @@
         <v>19900</v>
       </c>
       <c r="H49" s="3">
+        <v>19900</v>
+      </c>
+      <c r="I49" s="3">
         <v>20400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>21200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>24400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>25200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>26000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>26800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,8 +2684,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2576,22 +2696,22 @@
         <v>600</v>
       </c>
       <c r="E52" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F52" s="3">
         <v>500</v>
       </c>
       <c r="G52" s="3">
+        <v>500</v>
+      </c>
+      <c r="H52" s="3">
         <v>100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>200</v>
       </c>
       <c r="I52" s="3">
         <v>200</v>
       </c>
       <c r="J52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K52" s="3">
         <v>300</v>
@@ -2599,8 +2719,8 @@
       <c r="L52" s="3">
         <v>300</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
+      <c r="M52" s="3">
+        <v>300</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
@@ -2614,8 +2734,11 @@
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,55 +2784,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>275300</v>
+      </c>
+      <c r="E54" s="3">
         <v>302200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>319800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>268100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>275500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>124500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>141600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>142100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>155500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>170000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>180900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>134300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>149200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>164000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>178600</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,55 +2876,59 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2817,13 +2951,13 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>100</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -2840,125 +2974,134 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E59" s="3">
         <v>24000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>30700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>47700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>25200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E60" s="3">
         <v>38800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>41800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>65300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>31200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>24100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>17900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E61" s="3">
         <v>21900</v>
-      </c>
-      <c r="E61" s="3">
-        <v>24300</v>
       </c>
       <c r="F61" s="3">
         <v>24300</v>
       </c>
       <c r="G61" s="3">
+        <v>24300</v>
+      </c>
+      <c r="H61" s="3">
         <v>14200</v>
-      </c>
-      <c r="H61" s="3">
-        <v>14100</v>
       </c>
       <c r="I61" s="3">
         <v>14100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>14100</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2981,8 +3124,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2995,29 +3141,29 @@
       <c r="F62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H62" s="3">
         <v>0</v>
       </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1300</v>
-      </c>
-      <c r="N62" s="3">
-        <v>1900</v>
       </c>
       <c r="O62" s="3">
         <v>1900</v>
@@ -3026,10 +3172,13 @@
         <v>1900</v>
       </c>
       <c r="Q62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R62" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,55 +3324,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E66" s="3">
         <v>60700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>57600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>66100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>79500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>46400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>45600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>36100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>27300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,55 +3594,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-422200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-398900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-364100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-350500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-344600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-290200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-266300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-248400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-219300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-194500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-189600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-173100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-156100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-137700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-94000</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,55 +3794,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>222800</v>
+      </c>
+      <c r="E76" s="3">
         <v>241400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>262200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>202000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>196100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>78100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>96000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>106000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>130300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>150900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>153600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>124500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>136800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>151700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>166000</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-34700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-54400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-23900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-29100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-24800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-17000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-93000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,13 +4021,14 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -3837,23 +4036,23 @@
       <c r="F83" s="3">
         <v>0</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
-        <v>800</v>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>800</v>
@@ -3865,13 +4064,16 @@
         <v>800</v>
       </c>
       <c r="P83" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q83" s="3">
         <v>2600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-25400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-17200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-20000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-16600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-20600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-16600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-12800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-10800</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,8 +4391,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4200,8 +4421,8 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -4218,8 +4439,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,13 +4539,16 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>-162500</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>4</v>
@@ -4341,8 +4571,8 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -4354,13 +4584,16 @@
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,8 +4611,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4407,8 +4641,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4425,8 +4659,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,55 +4809,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E100" s="3">
         <v>3800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>69400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>169200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>17400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>58200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>98800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4625,86 +4874,92 @@
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-190900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-21500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>52200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>152600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>48800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-14700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>53400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-11200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MNMD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNMD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
   <si>
     <t>MNMD</t>
   </si>
@@ -656,87 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -767,8 +771,8 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -785,8 +789,11 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -835,8 +842,11 @@
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -885,8 +895,11 @@
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,58 +918,62 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E12" s="3">
         <v>23400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>21800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>17200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>13200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>14800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>8500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>9400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>34800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>15300</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,26 +1022,29 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>-2500</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1040,11 +1060,11 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
@@ -1052,11 +1072,14 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1073,11 +1096,11 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>500</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
@@ -1088,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="N15" s="3">
         <v>800</v>
@@ -1099,14 +1122,17 @@
       <c r="P15" s="3">
         <v>800</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R15" s="3">
+      <c r="Q15" s="3">
+        <v>800</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E17" s="3">
         <v>32200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>32500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24500</v>
-      </c>
-      <c r="H17" s="3">
-        <v>22200</v>
       </c>
       <c r="I17" s="3">
         <v>22200</v>
       </c>
       <c r="J17" s="3">
+        <v>22200</v>
+      </c>
+      <c r="K17" s="3">
         <v>21600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>29200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>20900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>93900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>17200</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-40900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-32200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-32500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-24800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-24500</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-22200</v>
       </c>
       <c r="I18" s="3">
         <v>-22200</v>
       </c>
       <c r="J18" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-21600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-29200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-20900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-17000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-16900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-93900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,140 +1275,147 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-7000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-8300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-13400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>33400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>9000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-25200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-37400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-16500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-55100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-24800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-19100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-30400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-26100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-15700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-16100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-17700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-91600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E22" s="3">
         <v>600</v>
-      </c>
-      <c r="E22" s="3">
-        <v>700</v>
       </c>
       <c r="F22" s="3">
         <v>700</v>
       </c>
       <c r="G22" s="3">
+        <v>700</v>
+      </c>
+      <c r="H22" s="3">
         <v>500</v>
-      </c>
-      <c r="H22" s="3">
-        <v>400</v>
       </c>
       <c r="I22" s="3">
         <v>400</v>
       </c>
       <c r="J22" s="3">
+        <v>400</v>
+      </c>
+      <c r="K22" s="3">
         <v>300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
+      <c r="M22" s="3">
+        <v>100</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>4</v>
@@ -1383,8 +1423,8 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1392,58 +1432,64 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-23300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-34700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-54400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-23900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-29100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-17000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-94200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1474,8 +1520,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1483,17 +1529,20 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3">
         <v>-1200</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-23300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-34700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-54400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-23900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-29100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-16500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-17000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-93000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-54400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-23900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-29100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-17000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-93000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>7000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>8300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>13400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-33400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-9000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-34700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-54400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-23900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-29100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-24800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-17000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-93000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-34700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-54400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-23900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-29100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-24800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-17000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-93000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,67 +2223,71 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E41" s="3">
         <v>82900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>273700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>295300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>243100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>252300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>99700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>117700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>116900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>129400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>142100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>154500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>105700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>120500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>133500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>145900</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>149600</v>
+      </c>
+      <c r="E42" s="3">
         <v>129600</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -2237,8 +2327,11 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2269,8 +2362,8 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2287,8 +2380,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2319,8 +2415,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2337,8 +2433,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2369,85 +2468,91 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>3900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>189100</v>
+      </c>
+      <c r="E46" s="3">
         <v>221700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>281600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>299400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>247700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>255500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>103900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>120100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>119800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>132400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>146100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>156500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>109100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>123200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>137200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>146500</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E47" s="3">
         <v>33100</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2469,8 +2574,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2487,8 +2592,11 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2519,8 +2627,8 @@
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -2531,14 +2639,17 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R48" s="3">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S48" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2558,37 +2669,40 @@
         <v>19900</v>
       </c>
       <c r="I49" s="3">
+        <v>19900</v>
+      </c>
+      <c r="J49" s="3">
         <v>20400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>21200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>23600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>24400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>25200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>26000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>26800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,34 +2804,37 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="E52" s="3">
         <v>600</v>
       </c>
       <c r="F52" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G52" s="3">
         <v>500</v>
       </c>
       <c r="H52" s="3">
+        <v>500</v>
+      </c>
+      <c r="I52" s="3">
         <v>100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>200</v>
       </c>
       <c r="J52" s="3">
         <v>200</v>
       </c>
       <c r="K52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L52" s="3">
         <v>300</v>
@@ -2722,8 +2842,8 @@
       <c r="M52" s="3">
         <v>300</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
+      <c r="N52" s="3">
+        <v>300</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>4</v>
@@ -2737,8 +2857,11 @@
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>265100</v>
+      </c>
+      <c r="E54" s="3">
         <v>275300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>302200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>319800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>268100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>275500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>124500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>141600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>142100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>155500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>170000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>180900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>134300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>149200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>164000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>178600</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,58 +3007,62 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E57" s="3">
         <v>2300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2954,13 +3088,13 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3">
         <v>100</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2977,134 +3111,143 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E59" s="3">
         <v>16700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>24000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>30700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>47700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>25200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E60" s="3">
         <v>30500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>41800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>65300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>31200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>24100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E61" s="3">
         <v>22000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>21900</v>
-      </c>
-      <c r="F61" s="3">
-        <v>24300</v>
       </c>
       <c r="G61" s="3">
         <v>24300</v>
       </c>
       <c r="H61" s="3">
+        <v>24300</v>
+      </c>
+      <c r="I61" s="3">
         <v>14200</v>
-      </c>
-      <c r="I61" s="3">
-        <v>14100</v>
       </c>
       <c r="J61" s="3">
         <v>14100</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>14100</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -3127,13 +3270,16 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>4</v>
+      <c r="D62" s="3">
+        <v>500</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>4</v>
@@ -3144,29 +3290,29 @@
       <c r="G62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1300</v>
-      </c>
-      <c r="O62" s="3">
-        <v>1900</v>
       </c>
       <c r="P62" s="3">
         <v>1900</v>
@@ -3175,10 +3321,13 @@
         <v>1900</v>
       </c>
       <c r="R62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="S62" s="3">
         <v>6800</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>79700</v>
+      </c>
+      <c r="E66" s="3">
         <v>52500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>60700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>57600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>66100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>79500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>46400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-465000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-422200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-398900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-364100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-350500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-344600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-290200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-266300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-248400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-219300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-194500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-189600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-173100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-156100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-137700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-94000</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>185400</v>
+      </c>
+      <c r="E76" s="3">
         <v>222800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>241400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>262200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>202000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>196100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>78100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>96000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>106000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>130300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>150900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>153600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>124500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>136800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>151700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>166000</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-34700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-54400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-23900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-29100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-24800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-17000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-93000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-17200</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,16 +4220,17 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -4039,23 +4238,23 @@
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>800</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>800</v>
@@ -4067,13 +4266,16 @@
         <v>800</v>
       </c>
       <c r="Q83" s="3">
+        <v>800</v>
+      </c>
+      <c r="R83" s="3">
         <v>2600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-29400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-25400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-17200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-20000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-16600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-20600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-16600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-12800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-15100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-45800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10800</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4424,8 +4645,8 @@
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -4442,8 +4663,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,17 +4769,20 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-162500</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F94" s="3" t="s">
         <v>4</v>
       </c>
@@ -4574,8 +4804,8 @@
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -4587,13 +4817,16 @@
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4644,8 +4878,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4662,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,58 +5055,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E100" s="3">
         <v>1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>69400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>10800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>169200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>17400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>58200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>98800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4877,89 +5126,95 @@
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-49500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-190900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-21500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>52200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>152600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>48800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-14700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>53400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11200</v>
       </c>
     </row>
